--- a/day1_excel_data_analyst_challenge.xlsx
+++ b/day1_excel_data_analyst_challenge.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srava\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A0E365-CE63-4C1D-B7D5-4E96A063EF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE91083-A513-489F-AFEE-E5BDB4178F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Challenge_Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="region revenue" sheetId="4" r:id="rId2"/>
     <sheet name="category wise revenue" sheetId="5" r:id="rId3"/>
     <sheet name="top5 products" sheetId="6" r:id="rId4"/>
-    <sheet name="Sales_Data" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
+    <sheet name="Sales_Data" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -874,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,7 +891,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1691,6 +1691,1101 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[day1_excel_data_analyst_challenge.xlsx]region revenue!PivotTable1</c:name>
+    <c:fmtId val="9"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'region revenue'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'region revenue'!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'region revenue'!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>116463</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>104808</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>108472</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>117043</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BB11-4423-A163-F03D788017DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1651954047"/>
+        <c:axId val="1651954527"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1651954047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1651954527"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1651954527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1651954047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[day1_excel_data_analyst_challenge.xlsx]category wise revenue!PivotTable2</c:name>
+    <c:fmtId val="8"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'category wise revenue'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4087-4EC8-A172-CFCE8090F21E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4087-4EC8-A172-CFCE8090F21E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4087-4EC8-A172-CFCE8090F21E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'category wise revenue'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Stationery</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'category wise revenue'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>227030</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90635</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>129121</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4087-4EC8-A172-CFCE8090F21E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1732,6 +2827,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2793,6 +3968,1028 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2875,6 +5072,330 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C67B7A-AEDA-6460-7953-569D669FB8E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="693420" y="350520"/>
+          <a:ext cx="9098280" cy="6019800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E21E3A2E-6B2C-8372-A60D-1C618BB9E1A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="891540" y="1219200"/>
+          <a:ext cx="2293620" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C99479F2-6765-6FA6-127E-3BDC0065C2A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="853440" y="2849880"/>
+          <a:ext cx="2293620" cy="922020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F9D603C-67F6-3E10-25AF-5489DE30D096}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="861060" y="4084320"/>
+          <a:ext cx="2293620" cy="1287780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC6F22EC-33C7-4351-9866-0012248B0EB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A8E25FF-A0FA-4A20-81D3-94C364D18DE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Sravanthi Belide" refreshedDate="46097.500948726854" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="200" xr:uid="{D82DB7BD-A966-4568-A5EF-6B152130039C}">
   <cacheSource type="worksheet">
@@ -4937,7 +7458,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36FA069A-8296-467D-A5B9-137B194E0DAC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36FA069A-8296-467D-A5B9-137B194E0DAC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4994,8 +7515,17 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue." fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5018,7 +7548,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FD2CF14-E415-4E6D-91C6-4699060A20F4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FD2CF14-E415-4E6D-91C6-4699060A20F4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -5060,7 +7590,7 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Revenue." fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="4">
+  <chartFormats count="16">
     <chartFormat chart="5" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -5095,6 +7625,141 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="5" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="11">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5829,7 +8494,7 @@
       <c r="A4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4">
         <v>90635</v>
       </c>
     </row>
@@ -5837,7 +8502,7 @@
       <c r="A5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5">
         <v>78975</v>
       </c>
     </row>
@@ -5845,7 +8510,7 @@
       <c r="A6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>66018</v>
       </c>
     </row>
@@ -5853,7 +8518,7 @@
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>64187</v>
       </c>
     </row>
@@ -5861,7 +8526,7 @@
       <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>53108</v>
       </c>
     </row>
@@ -5869,7 +8534,7 @@
       <c r="A9" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>352923</v>
       </c>
     </row>
@@ -5879,6 +8544,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9306A5D5-BEBE-489C-914E-46FBB56BBD7A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H203"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
